--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,8 +538,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Regular price
-                  £10.00</t>
+          <t>£10.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -590,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -633,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -660,8 +659,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Regular price
-                  £11.30</t>
+          <t>£11.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -696,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>£12.83</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -712,27 +710,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -755,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -782,8 +780,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Regular price
-                  £14.60</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -818,7 +815,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -834,27 +831,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -877,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -904,8 +901,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Regular price
-                  £14.92</t>
+          <t>£14.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -956,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -999,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1026,8 +1022,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Regular price
-                  £18.99</t>
+          <t>£18.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1062,7 +1057,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>£21.46</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1078,27 +1073,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1121,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1148,8 +1143,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Regular price
-                  £20.70</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1200,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1243,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1270,8 +1264,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Regular price
-                  £20.90</t>
+          <t>£20.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1306,7 +1299,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1322,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1365,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1392,8 +1385,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Regular price
-                  £23.99</t>
+          <t>£23.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1444,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1487,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1514,8 +1506,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Regular price
-                  £25.99</t>
+          <t>£25.99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1566,27 +1557,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1609,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1636,8 +1627,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Regular price
-                  £25.90</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1688,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1731,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1758,8 +1748,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Regular price
-                  £35.10</t>
+          <t>£35.10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1810,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1853,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1880,8 +1869,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Regular price
-                  £31.40</t>
+          <t>£31.40</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1932,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1975,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2002,8 +1990,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Regular price
-                  £39.70</t>
+          <t>£39.70</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2033,7 +2020,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£40.04</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2054,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2097,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2175,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2218,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2245,8 +2232,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Regular price
-                  £38.30</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2281,7 +2267,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2297,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2340,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2367,8 +2353,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Regular price
-                  £695.00</t>
+          <t>£695.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2398,7 +2383,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2465,8 +2450,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Regular price
-                  £895.00</t>
+          <t>£895.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2517,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2638,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2681,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2759,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2880,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2923,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3001,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3101,7 +3085,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£44.09</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3122,27 +3106,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3165,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3243,27 +3227,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3286,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3364,27 +3348,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3485,27 +3469,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6769ce955+80021]
-	GetHandleVerifier [0x0x7ff6769ce9b0+80112]
-	(No symbol) [0x0x7ff67675060f]
-	(No symbol) [0x0x7ff6767a8854]
-	(No symbol) [0x0x7ff6767a8b1c]
-	(No symbol) [0x0x7ff6767fc927]
-	(No symbol) [0x0x7ff6767d126f]
-	(No symbol) [0x0x7ff6767f968a]
-	(No symbol) [0x0x7ff6767d1003]
-	(No symbol) [0x0x7ff6767995d1]
-	(No symbol) [0x0x7ff67679a3f3]
-	GetHandleVerifier [0x0x7ff676c8dd0d+2960461]
-	GetHandleVerifier [0x0x7ff676c87fca+2936586]
-	GetHandleVerifier [0x0x7ff676ca8a07+3070279]
-	GetHandleVerifier [0x0x7ff6769e843e+185214]
-	GetHandleVerifier [0x0x7ff6769efe8f+216527]
-	GetHandleVerifier [0x0x7ff6769d7b94+117460]
-	GetHandleVerifier [0x0x7ff6769d7d4f+117903]
-	GetHandleVerifier [0x0x7ff6769bdc28+11112]
+	GetHandleVerifier [0x0x7ff7ee44e955+80021]
+	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
+	(No symbol) [0x0x7ff7ee1d060f]
+	(No symbol) [0x0x7ff7ee228854]
+	(No symbol) [0x0x7ff7ee228b1c]
+	(No symbol) [0x0x7ff7ee27c927]
+	(No symbol) [0x0x7ff7ee25126f]
+	(No symbol) [0x0x7ff7ee27968a]
+	(No symbol) [0x0x7ff7ee251003]
+	(No symbol) [0x0x7ff7ee2195d1]
+	(No symbol) [0x0x7ff7ee21a3f3]
+	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
+	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
+	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
+	GetHandleVerifier [0x0x7ff7ee46843e+185214]
+	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
+	GetHandleVerifier [0x0x7ff7ee457b94+117460]
+	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
+	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3528,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£10.08</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -589,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£12.83</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -710,27 +710,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£16.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -831,27 +831,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -952,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£21.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1073,27 +1073,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1194,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£23.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1315,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1436,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1557,27 +1557,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1678,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1920,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£40.04</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2041,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2162,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£43.58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2283,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>£68.97</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£44.09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3106,27 +3106,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3227,27 +3227,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3348,27 +3348,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3469,27 +3469,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ee44e955+80021]
-	GetHandleVerifier [0x0x7ff7ee44e9b0+80112]
-	(No symbol) [0x0x7ff7ee1d060f]
-	(No symbol) [0x0x7ff7ee228854]
-	(No symbol) [0x0x7ff7ee228b1c]
-	(No symbol) [0x0x7ff7ee27c927]
-	(No symbol) [0x0x7ff7ee25126f]
-	(No symbol) [0x0x7ff7ee27968a]
-	(No symbol) [0x0x7ff7ee251003]
-	(No symbol) [0x0x7ff7ee2195d1]
-	(No symbol) [0x0x7ff7ee21a3f3]
-	GetHandleVerifier [0x0x7ff7ee70dd0d+2960461]
-	GetHandleVerifier [0x0x7ff7ee707fca+2936586]
-	GetHandleVerifier [0x0x7ff7ee728a07+3070279]
-	GetHandleVerifier [0x0x7ff7ee46843e+185214]
-	GetHandleVerifier [0x0x7ff7ee46fe8f+216527]
-	GetHandleVerifier [0x0x7ff7ee457b94+117460]
-	GetHandleVerifier [0x0x7ff7ee457d4f+117903]
-	GetHandleVerifier [0x0x7ff7ee43dc28+11112]
+	GetHandleVerifier [0x0x7ff78b09e955+80021]
+	GetHandleVerifier [0x0x7ff78b09e9b0+80112]
+	(No symbol) [0x0x7ff78ae2060f]
+	(No symbol) [0x0x7ff78ae78854]
+	(No symbol) [0x0x7ff78ae78b1c]
+	(No symbol) [0x0x7ff78aecc927]
+	(No symbol) [0x0x7ff78aea126f]
+	(No symbol) [0x0x7ff78aec968a]
+	(No symbol) [0x0x7ff78aea1003]
+	(No symbol) [0x0x7ff78ae695d1]
+	(No symbol) [0x0x7ff78ae6a3f3]
+	GetHandleVerifier [0x0x7ff78b35dd0d+2960461]
+	GetHandleVerifier [0x0x7ff78b357fca+2936586]
+	GetHandleVerifier [0x0x7ff78b378a07+3070279]
+	GetHandleVerifier [0x0x7ff78b0b843e+185214]
+	GetHandleVerifier [0x0x7ff78b0bfe8f+216527]
+	GetHandleVerifier [0x0x7ff78b0a7b94+117460]
+	GetHandleVerifier [0x0x7ff78b0a7d4f+117903]
+	GetHandleVerifier [0x0x7ff78b08dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
